--- a/data/kaspi-financials-2023-2025.xlsx
+++ b/data/kaspi-financials-2023-2025.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kaspi.kz key financials, 2023–2025 (₸ million unless stated)</t>
+          <t>Kaspi.kz key financials, 2023-2025 (₸ million unless stated)</t>
         </is>
       </c>
     </row>
